--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D92D20"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +91,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -454,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -464,6 +474,11 @@
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,7 +491,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-15</t>
+          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-16. 왼쪽은 지식DB 원문, 오른쪽 「화면」 열은 화면 한도(질문 32자 · 버튼 7자)에 맞춘 글자. 빨간 글씨는 원문에서 바뀐 곳. 뜻·경계값은 같음</t>
         </is>
       </c>
     </row>
@@ -514,6 +529,31 @@
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>언제 나오나</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>화면 질문</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>화면 선택지 1</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>화면 선택지 2</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>화면 선택지 3</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>보조 문구</t>
         </is>
       </c>
     </row>
@@ -551,6 +591,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>없었어요</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>1~2일</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>3일 이상</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -586,6 +651,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>10분 미만</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>10~30분</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>30분 이상</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -621,6 +711,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>없었어요</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>1일</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>2일 이상</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -656,6 +771,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>90분 미만</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>90~150분</t>
+        </is>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>150분 넘게</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="inlineStr">
+        <is>
+          <t>예) 빠르게 걷기 · 자전거 · 계단 오르기</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -691,6 +831,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>안 했어요</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>150분 이하</t>
+        </is>
+      </c>
+      <c r="K9" s="7" t="inlineStr">
+        <is>
+          <t>150분 넘게</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="inlineStr">
+        <is>
+          <t>예) 달리기 · 등산 · 수영</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -726,6 +891,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="inlineStr">
+        <is>
+          <t>1번 이하</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>2~3번</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
+        <is>
+          <t>4번 이상</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>예) 스쿼트 · 아령 · 팔굽혀펴기</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -761,6 +951,31 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>반도 안 돼요</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>조금 줄었어요</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr">
+        <is>
+          <t>줄지 않았어요</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>걷기와 운동을 모두 합쳐 생각해 주세요</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -796,6 +1011,27 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>7시간 미만</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>7~9시간</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr">
+        <is>
+          <t>9시간 넘게</t>
+        </is>
+      </c>
+      <c r="L12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -831,6 +1067,27 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>거의 같아요</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>1~2시간</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr">
+        <is>
+          <t>2시간 이상</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -866,6 +1123,27 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>7시간 미만</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>7~9시간</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>9시간 넘게</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -901,6 +1179,27 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>거의 같아요</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>1~2시간</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr">
+        <is>
+          <t>2시간 이상</t>
+        </is>
+      </c>
+      <c r="L15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -936,7 +1235,29 @@
           <t>회복 중이거나 몸 상태를 알아야 하는 날, 최근 답이 없을 때만</t>
         </is>
       </c>
-    </row>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>오늘은 얼마나 피곤하세요?</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>괜찮아요</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>조금 피곤해요</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>많이 피곤해요</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,6 +40,7 @@
       <b val="1"/>
       <color rgb="00D92D20"/>
     </font>
+    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -80,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +98,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -491,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-16. 왼쪽은 지식DB 원문, 오른쪽 「화면」 열은 화면 한도(질문 32자 · 버튼 7자)에 맞춘 글자. 빨간 글씨는 원문에서 바뀐 곳. 뜻·경계값은 같음</t>
+          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-16. 왼쪽은 지식DB 원문, 오른쪽 「화면」 열은 화면에 맞게 다듬은 글자. 빨간 글씨는 원문에서 바뀐 곳. 뜻·경계값은 같음</t>
         </is>
       </c>
     </row>
@@ -593,10 +597,10 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날은 며칠인가요?</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>없었어요</t>
         </is>
@@ -653,7 +657,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>어제는 숨이 조금 찰 만큼 몇 분 움직이셨어요?</t>
+          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -716,7 +720,7 @@
           <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>없었어요</t>
         </is>
@@ -773,7 +777,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 조금 찰 만큼 모두 몇 분 움직이셨어요?</t>
+          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -833,12 +837,12 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 숨이 많이 찰 만큼 모두 몇 분 운동하셨어요?</t>
+          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>안 했어요</t>
+          <t>하지 않았어요</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -893,7 +897,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨어요?</t>
+          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -953,22 +957,22 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 평소와 비교해 얼마나 움직이셨어요?</t>
+          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>반도 안 돼요</t>
+          <t>절반도 안 됐어요</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>조금 줄었어요</t>
+          <t>조금 적었어요</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>줄지 않았어요</t>
+          <t>평소만큼 했어요</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1013,7 +1017,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>어젯밤엔 몇 시간 주무셨어요?</t>
+          <t>어젯밤에는 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1031,7 +1035,7 @@
           <t>9시간 넘게</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
+      <c r="L12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -1069,17 +1073,17 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>최근 3일, 자고 일어나는 시각이 날마다 얼마나 달랐나요?</t>
+          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>거의 같아요</t>
+          <t>거의 같았어요</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>1~2시간</t>
+          <t>1~2시간 정도</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1087,7 +1091,7 @@
           <t>2시간 이상</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr"/>
+      <c r="L13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1125,7 +1129,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 보통 몇 시간 주무셨어요?</t>
+          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1143,7 +1147,7 @@
           <t>9시간 넘게</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr"/>
+      <c r="L14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1181,17 +1185,17 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>최근 7일, 주무신 시간이 날마다 얼마나 달랐나요?</t>
+          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>거의 같아요</t>
+          <t>거의 같았어요</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1~2시간</t>
+          <t>1~2시간 정도</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1199,7 +1203,7 @@
           <t>2시간 이상</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -1237,25 +1241,25 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>오늘은 얼마나 피곤하세요?</t>
+          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>괜찮아요</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+          <t>피곤하지 않아요</t>
+        </is>
+      </c>
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>조금 피곤해요</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>많이 피곤해요</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr"/>
+      <c r="L16" s="8" t="inlineStr"/>
     </row>
     <row r="17"/>
   </sheetData>

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -600,9 +600,9 @@
           <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>없었어요</t>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="J5" s="7" t="inlineStr">
@@ -720,9 +720,9 @@
           <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
-        <is>
-          <t>없었어요</t>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>하지 않았어요</t>
+          <t>안 함</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -962,17 +962,17 @@
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>절반도 안 됐어요</t>
+          <t>절반 미만</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>조금 적었어요</t>
+          <t>조금 적음</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>평소만큼 했어요</t>
+          <t>평소만큼</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>거의 같았어요</t>
+          <t>거의 같음</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>1~2시간 정도</t>
+          <t>1~2시간</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>거의 같았어요</t>
+          <t>거의 같음</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1~2시간 정도</t>
+          <t>1~2시간</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
@@ -1246,17 +1246,17 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>피곤하지 않아요</t>
-        </is>
-      </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>조금 피곤해요</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="inlineStr">
-        <is>
-          <t>많이 피곤해요</t>
+          <t>피곤하지 않음</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>조금 피곤함</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>많이 피곤함</t>
         </is>
       </c>
       <c r="L16" s="8" t="inlineStr"/>

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -495,7 +495,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-16. 왼쪽은 지식DB 원문, 오른쪽 「화면」 열은 화면에 맞게 다듬은 글자. 빨간 글씨는 원문에서 바뀐 곳. 뜻·경계값은 같음</t>
+          <t>출처: 관리자 콘솔 지식DB 사용 중 판(2026-10-08_3) SQL 내보내기 · 질문 12개 · 선택지 36개 · 정리일 2026-10-16. 왼쪽은 지식DB 원문, 오른쪽 「화면」 열은 화면에 맞게 다듬은 글자. 빨간 글씨는 원문에서 바뀐 곳. 뜻·경계값은 같음 · 화면 질문은 지식DB 원문 그대로, 화면 선택지만 버튼에 맞게 줄임(뜻 · 경계값은 같음). 빨간 글씨는 원문에서 바뀐 선택지</t>
         </is>
       </c>
     </row>
@@ -595,9 +595,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 날은 며칠이었나요?</t>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 날이 며칠 있었나요?</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -655,9 +655,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>어제는 숨이 조금 찰 정도로 몇 분쯤 움직이셨나요?</t>
+      <c r="H6" s="8" t="inlineStr">
+        <is>
+          <t>어제 숨이 조금 찰 만큼 움직인 시간은 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -715,9 +715,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동을 한 날은 며칠이었나요?</t>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 한 날이 며칠 있었나요?</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -775,9 +775,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 조금 찰 정도로 움직인 시간은 모두 얼마나 되나요?</t>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 조금 찰 만큼 움직인 시간은 모두 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
@@ -835,9 +835,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 숨이 많이 찰 정도로 운동한 시간은 모두 얼마나 되나요?</t>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 숨이 많이 찰 만큼 운동한 시간은 모두 얼마나 됐나요?</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -895,9 +895,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 근력 운동은 몇 번 하셨나요?</t>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 근육을 쓰는 운동을 몇 번 했나요?</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
@@ -955,9 +955,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 걷거나 운동한 시간은 평소와 비교해 어땠나요?</t>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 걷거나 운동한 시간은 평소의 절반과 비교해 어땠나요?</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -967,12 +967,12 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>조금 적음</t>
+          <t>절반~평소</t>
         </is>
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>평소만큼</t>
+          <t>평소 이상</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1015,9 +1015,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>어젯밤에는 몇 시간 주무셨나요?</t>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>어젯밤 잠은 몇 시간 정도 주무셨나요?</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -1071,9 +1071,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>최근 3일, 잠들고 일어나는 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>최근 3일, 잠든 시간과 일어난 시간이 얼마나 비슷했나요?</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1127,9 +1127,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 하루에 보통 몇 시간 주무셨나요?</t>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 하루에 잠은 대체로 몇 시간 잤나요?</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1183,9 +1183,9 @@
           <t>워치·건강 앱으로 그 값을 잴 수 없을 때만</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>최근 7일, 주무신 시간은 날마다 얼마나 달랐나요?</t>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>최근 7일, 잠잔 시간은 날마다 얼마나 달랐나요?</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -1239,9 +1239,9 @@
           <t>회복 중이거나 몸 상태를 알아야 하는 날, 최근 답이 없을 때만</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>오늘은 몸이 얼마나 피곤하신가요?</t>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>오늘은 피로감이 어느 정도인가요?</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -499,6 +499,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -967,13 +968,11 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>절반~평소</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>평소 이상</t>
-        </is>
+          <t>절반~평소 사이</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1261,7 +1260,6 @@
       </c>
       <c r="L16" s="8" t="inlineStr"/>
     </row>
-    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -1082,13 +1082,11 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>1~2시간</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>2시간 이상</t>
-        </is>
+          <t>1~2시간 차이남</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>9</v>
       </c>
       <c r="L13" s="8" t="inlineStr"/>
     </row>

--- a/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
+++ b/docs/엔진/코칭목표/지식DB/maiReport_지식DB_자가응답질문_선택지_v1.0.0.xlsx
@@ -1192,13 +1192,11 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>1~2시간</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>2시간 이상</t>
-        </is>
+          <t>1~2시간 차이남</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="n">
+        <v>8</v>
       </c>
       <c r="L15" s="8" t="inlineStr"/>
     </row>
